--- a/expense_reimburse_rpa/files/费用报销rpa配置表.xlsx
+++ b/expense_reimburse_rpa/files/费用报销rpa配置表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\xc\expense_reimburse_rpa\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFA815C-EF7D-442C-AFA1-BC91371DFF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE63648D-2C8E-4CFB-8A80-3FB8E8E1EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33495" yWindow="4575" windowWidth="17925" windowHeight="8850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36555" yWindow="3600" windowWidth="17985" windowHeight="10620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务商对应表" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>服务商名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,10 +92,6 @@
   </si>
   <si>
     <t>lishuaiae</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mm2002902L.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -613,82 +609,82 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
       </c>
       <c r="C2">
         <v>123456</v>
       </c>
       <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>123457</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>123458</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>123459</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -712,13 +708,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -749,30 +745,27 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -780,89 +773,89 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
         <v>2001270</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
